--- a/InputData/trans/ANVCV/Additional New Vehicles Calibration Variable.xlsx
+++ b/InputData/trans/ANVCV/Additional New Vehicles Calibration Variable.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\trans\ANVCV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\EPS Structure Research\eps-us-calibration\InputData\trans\ANVCV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7C65778-ACE1-4F90-8235-4F800CB7F99C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F48FE5F-02D6-475A-815D-6637C474FFA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2040" yWindow="2100" windowWidth="24420" windowHeight="14370" xr2:uid="{DC12087C-9A27-4A43-B4A9-6B3F1E517F08}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="10008" activeTab="1" xr2:uid="{DC12087C-9A27-4A43-B4A9-6B3F1E517F08}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="ANVCV-psgr" sheetId="2" r:id="rId2"/>
-    <sheet name="ANVCV-frgt" sheetId="6" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="7" r:id="rId2"/>
+    <sheet name="ANVCV-psgr" sheetId="2" r:id="rId3"/>
+    <sheet name="ANVCV-frgt" sheetId="6" r:id="rId4"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId4"/>
+    <externalReference r:id="rId5"/>
   </externalReferences>
   <definedNames>
     <definedName name="asdf">#REF!</definedName>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="27">
   <si>
     <t>Sources:</t>
   </si>
@@ -79,10 +80,55 @@
     <t xml:space="preserve">This variable can adjust sales of new vehicles in historical years to aid in calibration. </t>
   </si>
   <si>
-    <t>The sum of each row should be zero.</t>
+    <t>vehicles</t>
   </si>
   <si>
-    <t>vehicles</t>
+    <t>ANVCV: additional new vehicles that put total LDV sales on the benchmark path (pinned mode)</t>
+  </si>
+  <si>
+    <t>In the model, New Vehicles Demanded = SoCDTtiNTY x cargo distance / BAADTbVT + ANVCV. Column C is the distance-driven term D(t) (vehicles the share formula sells per unit share), taken from the final confirming run as (New Vehicles Demanded - ANVCV) / SoCDTtiNTY. Column B is the sales target: MarkLines light-vehicle sales through the start year, then the AEO 2026 Alternative Electricity and Transportation case's shape at the start-year level (calibration/benchmarks/vehicle-sales.csv, vehicle-sales-projection.csv). ANVCV = target - share x D. Rows no longer sum to zero: ANVCV is stock-neutral only while the flat retirement window lasts and is a sales-only lever after the handoff. Non-LDV rows stay zero (no public sales history in scope).</t>
+  </si>
+  <si>
+    <t>LDVs / passenger</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Sales target (vehicles)</t>
+  </si>
+  <si>
+    <t>Distance-driven demand per unit share D(t) (vehicles), from run r2_final</t>
+  </si>
+  <si>
+    <t>SoCDTtiNTY share</t>
+  </si>
+  <si>
+    <t>ANVCV = target - share x D  (USED IN THE OUTPUT TAB)</t>
+  </si>
+  <si>
+    <t>Modelled sales, run r2_final</t>
+  </si>
+  <si>
+    <t>LDVs / freight</t>
+  </si>
+  <si>
+    <t>Rows need not sum to zero. ANVCV is stock-neutral only during the flat retirement window (it adds equally to sales and retirements); after the handoff it moves sales only.</t>
+  </si>
+  <si>
+    <t>Calibration record (2026-09-22)</t>
+  </si>
+  <si>
+    <t>LDV rows now come from the Calibration tab (calibration/steps/01-trans-turnover/solve.py, pinned mode, confirmed by run):</t>
+  </si>
+  <si>
+    <t>ANVCV = benchmark sales target - SoCDTtiNTY x distance-driven demand, every year 2025-2050.</t>
+  </si>
+  <si>
+    <t>Consequence recorded in calibration/calibration-log.md: sales sit on the benchmark; the LDV stock runs ~16% below</t>
+  </si>
+  <si>
+    <t>AEO by 2050 and implied miles per vehicle ~27% above BAADTbVT, with no effect on fuel or emissions (cargo distance is exogenous).</t>
   </si>
 </sst>
 </file>
@@ -134,13 +180,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -163,6 +215,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="About"/>
@@ -547,39 +600,64 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF982137-6F01-4109-8226-D4C6F3731BA9}">
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.42578125" customWidth="1"/>
-    <col min="2" max="2" width="101.28515625" customWidth="1"/>
+    <col min="1" max="1" width="19.44140625" customWidth="1"/>
+    <col min="2" max="2" width="101.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" s="2"/>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -588,19 +666,1192 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC86FBD8-3E4E-4C67-89F8-CE780820B2E8}">
+  <dimension ref="A1:F61"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="6" width="22.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="109.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>2025</v>
+      </c>
+      <c r="B6">
+        <v>14793201</v>
+      </c>
+      <c r="C6">
+        <v>266628054.91802782</v>
+      </c>
+      <c r="D6">
+        <v>5.2610446429999999E-2</v>
+      </c>
+      <c r="E6">
+        <f>B6-D6*C6</f>
+        <v>765780</v>
+      </c>
+      <c r="F6">
+        <v>14793201</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>2026</v>
+      </c>
+      <c r="B7">
+        <v>14386353</v>
+      </c>
+      <c r="C7">
+        <v>269320847.12211025</v>
+      </c>
+      <c r="D7">
+        <v>5.2610446429999999E-2</v>
+      </c>
+      <c r="E7">
+        <f>B7-D7*C7</f>
+        <v>217263</v>
+      </c>
+      <c r="F7">
+        <v>14386353</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>2027</v>
+      </c>
+      <c r="B8">
+        <v>14832541</v>
+      </c>
+      <c r="C8">
+        <v>272339202.04542923</v>
+      </c>
+      <c r="D8">
+        <v>5.2610446429999999E-2</v>
+      </c>
+      <c r="E8">
+        <f>B8-D8*C8</f>
+        <v>504654</v>
+      </c>
+      <c r="F8">
+        <v>14832541</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>2028</v>
+      </c>
+      <c r="B9">
+        <v>15006158</v>
+      </c>
+      <c r="C9">
+        <v>275469625.96644896</v>
+      </c>
+      <c r="D9">
+        <v>5.2610446429999999E-2</v>
+      </c>
+      <c r="E9">
+        <f>B9-D9*C9</f>
+        <v>513578</v>
+      </c>
+      <c r="F9">
+        <v>15006158</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>2029</v>
+      </c>
+      <c r="B10">
+        <v>15310873</v>
+      </c>
+      <c r="C10">
+        <v>278796531.7784512</v>
+      </c>
+      <c r="D10">
+        <v>5.2610446429999999E-2</v>
+      </c>
+      <c r="E10">
+        <f>B10-D10*C10</f>
+        <v>643263</v>
+      </c>
+      <c r="F10">
+        <v>15310873</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>2030</v>
+      </c>
+      <c r="B11">
+        <v>15769710</v>
+      </c>
+      <c r="C11">
+        <v>282464472.52205914</v>
+      </c>
+      <c r="D11">
+        <v>5.2610446429999999E-2</v>
+      </c>
+      <c r="E11">
+        <f>B11-D11*C11</f>
+        <v>909128</v>
+      </c>
+      <c r="F11">
+        <v>15769710</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>2031</v>
+      </c>
+      <c r="B12">
+        <v>16000009</v>
+      </c>
+      <c r="C12">
+        <v>286223744.93696159</v>
+      </c>
+      <c r="D12">
+        <v>5.2610446429999999E-2</v>
+      </c>
+      <c r="E12">
+        <f>B12-D12*C12</f>
+        <v>941649.99999999814</v>
+      </c>
+      <c r="F12">
+        <v>16000009</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>2032</v>
+      </c>
+      <c r="B13">
+        <v>16117749</v>
+      </c>
+      <c r="C13">
+        <v>289930841.40228993</v>
+      </c>
+      <c r="D13">
+        <v>5.2610446429999999E-2</v>
+      </c>
+      <c r="E13">
+        <f>B13-D13*C13</f>
+        <v>864358</v>
+      </c>
+      <c r="F13">
+        <v>16117749</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>2033</v>
+      </c>
+      <c r="B14">
+        <v>16282723</v>
+      </c>
+      <c r="C14">
+        <v>293690893.13010037</v>
+      </c>
+      <c r="D14">
+        <v>5.2610446429999999E-2</v>
+      </c>
+      <c r="E14">
+        <f>B14-D14*C14</f>
+        <v>831514</v>
+      </c>
+      <c r="F14">
+        <v>16282723</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>2034</v>
+      </c>
+      <c r="B15">
+        <v>16320812</v>
+      </c>
+      <c r="C15">
+        <v>297280693.49895459</v>
+      </c>
+      <c r="D15">
+        <v>5.2610446429999999E-2</v>
+      </c>
+      <c r="E15">
+        <f>B15-D15*C15</f>
+        <v>680742</v>
+      </c>
+      <c r="F15">
+        <v>16320812</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>2035</v>
+      </c>
+      <c r="B16">
+        <v>16367287</v>
+      </c>
+      <c r="C16">
+        <v>300780625.78417093</v>
+      </c>
+      <c r="D16">
+        <v>5.2610446429999999E-2</v>
+      </c>
+      <c r="E16">
+        <f>B16-D16*C16</f>
+        <v>543083.99999999814</v>
+      </c>
+      <c r="F16">
+        <v>16367287</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>2036</v>
+      </c>
+      <c r="B17">
+        <v>16136078</v>
+      </c>
+      <c r="C17">
+        <v>303957352.29650664</v>
+      </c>
+      <c r="D17">
+        <v>5.2610446429999999E-2</v>
+      </c>
+      <c r="E17">
+        <f>B17-D17*C17</f>
+        <v>144746</v>
+      </c>
+      <c r="F17">
+        <v>16136078</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>2037</v>
+      </c>
+      <c r="B18">
+        <v>16147860</v>
+      </c>
+      <c r="C18">
+        <v>307085685.37801707</v>
+      </c>
+      <c r="D18">
+        <v>5.2610446429999999E-2</v>
+      </c>
+      <c r="E18">
+        <f>B18-D18*C18</f>
+        <v>-8055.0000000018626</v>
+      </c>
+      <c r="F18">
+        <v>16147860</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>2038</v>
+      </c>
+      <c r="B19">
+        <v>16141978</v>
+      </c>
+      <c r="C19">
+        <v>310175566.02018744</v>
+      </c>
+      <c r="D19">
+        <v>5.2610446429999999E-2</v>
+      </c>
+      <c r="E19">
+        <f>B19-D19*C19</f>
+        <v>-176497</v>
+      </c>
+      <c r="F19">
+        <v>16141978</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>2039</v>
+      </c>
+      <c r="B20">
+        <v>16103017</v>
+      </c>
+      <c r="C20">
+        <v>313193920.94350642</v>
+      </c>
+      <c r="D20">
+        <v>5.2610446429999999E-2</v>
+      </c>
+      <c r="E20">
+        <f>B20-D20*C20</f>
+        <v>-374255</v>
+      </c>
+      <c r="F20">
+        <v>16103017</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>2040</v>
+      </c>
+      <c r="B21">
+        <v>16066682</v>
+      </c>
+      <c r="C21">
+        <v>316148258.16257572</v>
+      </c>
+      <c r="D21">
+        <v>5.2610446429999999E-2</v>
+      </c>
+      <c r="E21">
+        <f>B21-D21*C21</f>
+        <v>-566019</v>
+      </c>
+      <c r="F21">
+        <v>16066682</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>2041</v>
+      </c>
+      <c r="B22">
+        <v>15955861</v>
+      </c>
+      <c r="C22">
+        <v>318882715.09578979</v>
+      </c>
+      <c r="D22">
+        <v>5.2610446429999999E-2</v>
+      </c>
+      <c r="E22">
+        <f>B22-D22*C22</f>
+        <v>-820701</v>
+      </c>
+      <c r="F22">
+        <v>15955861</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>2042</v>
+      </c>
+      <c r="B23">
+        <v>15842787</v>
+      </c>
+      <c r="C23">
+        <v>321442815.02155656</v>
+      </c>
+      <c r="D23">
+        <v>5.2610446429999999E-2</v>
+      </c>
+      <c r="E23">
+        <f>B23-D23*C23</f>
+        <v>-1068463</v>
+      </c>
+      <c r="F23">
+        <v>15842787</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>2043</v>
+      </c>
+      <c r="B24">
+        <v>15750002</v>
+      </c>
+      <c r="C24">
+        <v>323788870.00446236</v>
+      </c>
+      <c r="D24">
+        <v>5.2610446429999999E-2</v>
+      </c>
+      <c r="E24">
+        <f>B24-D24*C24</f>
+        <v>-1284675</v>
+      </c>
+      <c r="F24">
+        <v>15750002</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>2044</v>
+      </c>
+      <c r="B25">
+        <v>15669295</v>
+      </c>
+      <c r="C25">
+        <v>325912896.83910787</v>
+      </c>
+      <c r="D25">
+        <v>5.2610446429999999E-2</v>
+      </c>
+      <c r="E25">
+        <f>B25-D25*C25</f>
+        <v>-1477128</v>
+      </c>
+      <c r="F25">
+        <v>15669295</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>2045</v>
+      </c>
+      <c r="B26">
+        <v>15623885</v>
+      </c>
+      <c r="C26">
+        <v>327808699.03749269</v>
+      </c>
+      <c r="D26">
+        <v>5.2610446429999999E-2</v>
+      </c>
+      <c r="E26">
+        <f>B26-D26*C26</f>
+        <v>-1622277</v>
+      </c>
+      <c r="F26">
+        <v>15623885</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>2046</v>
+      </c>
+      <c r="B27">
+        <v>15528804</v>
+      </c>
+      <c r="C27">
+        <v>329419367.74969882</v>
+      </c>
+      <c r="D27">
+        <v>5.2610446429999999E-2</v>
+      </c>
+      <c r="E27">
+        <f>B27-D27*C27</f>
+        <v>-1802096</v>
+      </c>
+      <c r="F27">
+        <v>15528804</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>2047</v>
+      </c>
+      <c r="B28">
+        <v>15466449</v>
+      </c>
+      <c r="C28">
+        <v>330791509.68915284</v>
+      </c>
+      <c r="D28">
+        <v>5.2610446429999999E-2</v>
+      </c>
+      <c r="E28">
+        <f>B28-D28*C28</f>
+        <v>-1936640</v>
+      </c>
+      <c r="F28">
+        <v>15466449</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>2048</v>
+      </c>
+      <c r="B29">
+        <v>15344954</v>
+      </c>
+      <c r="C29">
+        <v>331847516.69479418</v>
+      </c>
+      <c r="D29">
+        <v>5.2610446429999999E-2</v>
+      </c>
+      <c r="E29">
+        <f>B29-D29*C29</f>
+        <v>-2113692</v>
+      </c>
+      <c r="F29">
+        <v>15344954</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>2049</v>
+      </c>
+      <c r="B30">
+        <v>15211128</v>
+      </c>
+      <c r="C30">
+        <v>332686722.65094864</v>
+      </c>
+      <c r="D30">
+        <v>5.2610446429999999E-2</v>
+      </c>
+      <c r="E30">
+        <f>B30-D30*C30</f>
+        <v>-2291669</v>
+      </c>
+      <c r="F30">
+        <v>15211128</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>2050</v>
+      </c>
+      <c r="B31">
+        <v>14988471</v>
+      </c>
+      <c r="C31">
+        <v>333140529.86263549</v>
+      </c>
+      <c r="D31">
+        <v>5.2610446429999999E-2</v>
+      </c>
+      <c r="E31">
+        <f>B31-D31*C31</f>
+        <v>-2538201</v>
+      </c>
+      <c r="F31">
+        <v>14988471</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>2025</v>
+      </c>
+      <c r="B36">
+        <v>1724865</v>
+      </c>
+      <c r="C36">
+        <v>23955430.196154539</v>
+      </c>
+      <c r="D36">
+        <v>6.6346126409999998E-2</v>
+      </c>
+      <c r="E36">
+        <f>B36-D36*C36</f>
+        <v>135515</v>
+      </c>
+      <c r="F36">
+        <v>1724865</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>2026</v>
+      </c>
+      <c r="B37">
+        <v>1677426</v>
+      </c>
+      <c r="C37">
+        <v>23924395.980422392</v>
+      </c>
+      <c r="D37">
+        <v>6.6346126409999998E-2</v>
+      </c>
+      <c r="E37">
+        <f>B37-D37*C37</f>
+        <v>90135.000000000233</v>
+      </c>
+      <c r="F37">
+        <v>1677426</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>2027</v>
+      </c>
+      <c r="B38">
+        <v>1729464</v>
+      </c>
+      <c r="C38">
+        <v>23997482.387457442</v>
+      </c>
+      <c r="D38">
+        <v>6.6346126409999998E-2</v>
+      </c>
+      <c r="E38">
+        <f>B38-D38*C38</f>
+        <v>137324</v>
+      </c>
+      <c r="F38">
+        <v>1729464</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>2028</v>
+      </c>
+      <c r="B39">
+        <v>1749700</v>
+      </c>
+      <c r="C39">
+        <v>24120729.974655956</v>
+      </c>
+      <c r="D39">
+        <v>6.6346126409999998E-2</v>
+      </c>
+      <c r="E39">
+        <f>B39-D39*C39</f>
+        <v>149383</v>
+      </c>
+      <c r="F39">
+        <v>1749700</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>2029</v>
+      </c>
+      <c r="B40">
+        <v>1785235</v>
+      </c>
+      <c r="C40">
+        <v>24283165.983857173</v>
+      </c>
+      <c r="D40">
+        <v>6.6346126409999998E-2</v>
+      </c>
+      <c r="E40">
+        <f>B40-D40*C40</f>
+        <v>174141</v>
+      </c>
+      <c r="F40">
+        <v>1785235</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>2030</v>
+      </c>
+      <c r="B41">
+        <v>1838731</v>
+      </c>
+      <c r="C41">
+        <v>24492371.867471624</v>
+      </c>
+      <c r="D41">
+        <v>6.6346126409999998E-2</v>
+      </c>
+      <c r="E41">
+        <f>B41-D41*C41</f>
+        <v>213757</v>
+      </c>
+      <c r="F41">
+        <v>1838731</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>2031</v>
+      </c>
+      <c r="B42">
+        <v>1865591</v>
+      </c>
+      <c r="C42">
+        <v>24717720.366457187</v>
+      </c>
+      <c r="D42">
+        <v>6.6346126409999998E-2</v>
+      </c>
+      <c r="E42">
+        <f>B42-D42*C42</f>
+        <v>225666</v>
+      </c>
+      <c r="F42">
+        <v>1865591</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>2032</v>
+      </c>
+      <c r="B43">
+        <v>1879310</v>
+      </c>
+      <c r="C43">
+        <v>24986266.564465735</v>
+      </c>
+      <c r="D43">
+        <v>6.6346126409999998E-2</v>
+      </c>
+      <c r="E43">
+        <f>B43-D43*C43</f>
+        <v>221568</v>
+      </c>
+      <c r="F43">
+        <v>1879310</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>2033</v>
+      </c>
+      <c r="B44">
+        <v>1898535</v>
+      </c>
+      <c r="C44">
+        <v>25232731.593922757</v>
+      </c>
+      <c r="D44">
+        <v>6.6346126409999998E-2</v>
+      </c>
+      <c r="E44">
+        <f>B44-D44*C44</f>
+        <v>224441</v>
+      </c>
+      <c r="F44">
+        <v>1898535</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>2034</v>
+      </c>
+      <c r="B45">
+        <v>1902978</v>
+      </c>
+      <c r="C45">
+        <v>25460506.760578491</v>
+      </c>
+      <c r="D45">
+        <v>6.6346126409999998E-2</v>
+      </c>
+      <c r="E45">
+        <f>B45-D45*C45</f>
+        <v>213772</v>
+      </c>
+      <c r="F45">
+        <v>1902978</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>2035</v>
+      </c>
+      <c r="B46">
+        <v>1908404</v>
+      </c>
+      <c r="C46">
+        <v>25674776.994113289</v>
+      </c>
+      <c r="D46">
+        <v>6.6346126409999998E-2</v>
+      </c>
+      <c r="E46">
+        <f>B46-D46*C46</f>
+        <v>204982</v>
+      </c>
+      <c r="F46">
+        <v>1908404</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>2036</v>
+      </c>
+      <c r="B47">
+        <v>1881430</v>
+      </c>
+      <c r="C47">
+        <v>25871352.147866864</v>
+      </c>
+      <c r="D47">
+        <v>6.6346126409999998E-2</v>
+      </c>
+      <c r="E47">
+        <f>B47-D47*C47</f>
+        <v>164966</v>
+      </c>
+      <c r="F47">
+        <v>1881430</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>2037</v>
+      </c>
+      <c r="B48">
+        <v>1882809</v>
+      </c>
+      <c r="C48">
+        <v>26054000.33933948</v>
+      </c>
+      <c r="D48">
+        <v>6.6346126409999998E-2</v>
+      </c>
+      <c r="E48">
+        <f>B48-D48*C48</f>
+        <v>154227</v>
+      </c>
+      <c r="F48">
+        <v>1882809</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>2038</v>
+      </c>
+      <c r="B49">
+        <v>1882128</v>
+      </c>
+      <c r="C49">
+        <v>26223942.438601218</v>
+      </c>
+      <c r="D49">
+        <v>6.6346126409999998E-2</v>
+      </c>
+      <c r="E49">
+        <f>B49-D49*C49</f>
+        <v>142271</v>
+      </c>
+      <c r="F49">
+        <v>1882128</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>2039</v>
+      </c>
+      <c r="B50">
+        <v>1877592</v>
+      </c>
+      <c r="C50">
+        <v>26386393.520272437</v>
+      </c>
+      <c r="D50">
+        <v>6.6346126409999998E-2</v>
+      </c>
+      <c r="E50">
+        <f>B50-D50*C50</f>
+        <v>126957</v>
+      </c>
+      <c r="F50">
+        <v>1877592</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>2040</v>
+      </c>
+      <c r="B51">
+        <v>1873344</v>
+      </c>
+      <c r="C51">
+        <v>26534088.653812639</v>
+      </c>
+      <c r="D51">
+        <v>6.6346126409999998E-2</v>
+      </c>
+      <c r="E51">
+        <f>B51-D51*C51</f>
+        <v>112910</v>
+      </c>
+      <c r="F51">
+        <v>1873344</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>2041</v>
+      </c>
+      <c r="B52">
+        <v>1860429</v>
+      </c>
+      <c r="C52">
+        <v>26694881.763783745</v>
+      </c>
+      <c r="D52">
+        <v>6.6346126409999998E-2</v>
+      </c>
+      <c r="E52">
+        <f>B52-D52*C52</f>
+        <v>89327</v>
+      </c>
+      <c r="F52">
+        <v>1860429</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>2042</v>
+      </c>
+      <c r="B53">
+        <v>1847247</v>
+      </c>
+      <c r="C53">
+        <v>26859036.034565084</v>
+      </c>
+      <c r="D53">
+        <v>6.6346126409999998E-2</v>
+      </c>
+      <c r="E53">
+        <f>B53-D53*C53</f>
+        <v>65254</v>
+      </c>
+      <c r="F53">
+        <v>1847247</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>2043</v>
+      </c>
+      <c r="B54">
+        <v>1836429</v>
+      </c>
+      <c r="C54">
+        <v>27070698.730789702</v>
+      </c>
+      <c r="D54">
+        <v>6.6346126409999998E-2</v>
+      </c>
+      <c r="E54">
+        <f>B54-D54*C54</f>
+        <v>40393</v>
+      </c>
+      <c r="F54">
+        <v>1836429</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>2044</v>
+      </c>
+      <c r="B55">
+        <v>1827021</v>
+      </c>
+      <c r="C55">
+        <v>27311813.033396356</v>
+      </c>
+      <c r="D55">
+        <v>6.6346126409999998E-2</v>
+      </c>
+      <c r="E55">
+        <f>B55-D55*C55</f>
+        <v>14988</v>
+      </c>
+      <c r="F55">
+        <v>1827021</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>2045</v>
+      </c>
+      <c r="B56">
+        <v>1821720</v>
+      </c>
+      <c r="C56">
+        <v>27543597.477072362</v>
+      </c>
+      <c r="D56">
+        <v>6.6346126409999998E-2</v>
+      </c>
+      <c r="E56">
+        <f>B56-D56*C56</f>
+        <v>-5691</v>
+      </c>
+      <c r="F56">
+        <v>1821720</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>2046</v>
+      </c>
+      <c r="B57">
+        <v>1810641</v>
+      </c>
+      <c r="C57">
+        <v>27751672.925436735</v>
+      </c>
+      <c r="D57">
+        <v>6.6346126409999998E-2</v>
+      </c>
+      <c r="E57">
+        <f>B57-D57*C57</f>
+        <v>-30575</v>
+      </c>
+      <c r="F57">
+        <v>1810641</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>2047</v>
+      </c>
+      <c r="B58">
+        <v>1803378</v>
+      </c>
+      <c r="C58">
+        <v>27951850.399520561</v>
+      </c>
+      <c r="D58">
+        <v>6.6346126409999998E-2</v>
+      </c>
+      <c r="E58">
+        <f>B58-D58*C58</f>
+        <v>-51119</v>
+      </c>
+      <c r="F58">
+        <v>1803378</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>2048</v>
+      </c>
+      <c r="B59">
+        <v>1789200</v>
+      </c>
+      <c r="C59">
+        <v>28131755.401452985</v>
+      </c>
+      <c r="D59">
+        <v>6.6346126409999998E-2</v>
+      </c>
+      <c r="E59">
+        <f>B59-D59*C59</f>
+        <v>-77233</v>
+      </c>
+      <c r="F59">
+        <v>1789200</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>2049</v>
+      </c>
+      <c r="B60">
+        <v>1773600</v>
+      </c>
+      <c r="C60">
+        <v>28269774.009252518</v>
+      </c>
+      <c r="D60">
+        <v>6.6346126409999998E-2</v>
+      </c>
+      <c r="E60">
+        <f>B60-D60*C60</f>
+        <v>-101990</v>
+      </c>
+      <c r="F60">
+        <v>1773600</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>2050</v>
+      </c>
+      <c r="B61">
+        <v>1747638</v>
+      </c>
+      <c r="C61">
+        <v>28366976.368289232</v>
+      </c>
+      <c r="D61">
+        <v>6.6346126409999998E-2</v>
+      </c>
+      <c r="E61">
+        <f>B61-D61*C61</f>
+        <v>-134401</v>
+      </c>
+      <c r="F61">
+        <v>1747638</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB58F1CD-3AD5-4A1E-8AA0-C74AF29D4BF2}">
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AB7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" customWidth="1"/>
+    <col min="1" max="1" width="11.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B1">
         <v>2024</v>
@@ -684,93 +1935,120 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <f>Calibration!$E$6</f>
+        <v>765780</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <f>Calibration!$E$6</f>
+        <v>765780</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <f>Calibration!$E$7</f>
+        <v>217263</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <f>Calibration!$E$8</f>
+        <v>504654</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <f>Calibration!$E$9</f>
+        <v>513578</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <f>Calibration!$E$10</f>
+        <v>643263</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <f>Calibration!$E$11</f>
+        <v>909128</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <f>Calibration!$E$12</f>
+        <v>941649.99999999814</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <f>Calibration!$E$13</f>
+        <v>864358</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <f>Calibration!$E$14</f>
+        <v>831514</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <f>Calibration!$E$15</f>
+        <v>680742</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <f>Calibration!$E$16</f>
+        <v>543083.99999999814</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <f>Calibration!$E$17</f>
+        <v>144746</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <f>Calibration!$E$18</f>
+        <v>-8055.0000000018626</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <f>Calibration!$E$19</f>
+        <v>-176497</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <f>Calibration!$E$20</f>
+        <v>-374255</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <f>Calibration!$E$21</f>
+        <v>-566019</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <f>Calibration!$E$22</f>
+        <v>-820701</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <f>Calibration!$E$23</f>
+        <v>-1068463</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <f>Calibration!$E$24</f>
+        <v>-1284675</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <f>Calibration!$E$25</f>
+        <v>-1477128</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <f>Calibration!$E$26</f>
+        <v>-1622277</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <f>Calibration!$E$27</f>
+        <v>-1802096</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <f>Calibration!$E$28</f>
+        <v>-1936640</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <f>Calibration!$E$29</f>
+        <v>-2113692</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <f>Calibration!$E$30</f>
+        <v>-2291669</v>
       </c>
       <c r="AB2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+        <f>Calibration!$E$31</f>
+        <v>-2538201</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -856,7 +2134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -942,7 +2220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1028,7 +2306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1114,7 +2392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1205,20 +2483,20 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF5E5331-5AE2-4A88-8429-CB240947B731}">
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AB7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" customWidth="1"/>
+    <col min="1" max="1" width="11.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B1">
         <v>2024</v>
@@ -1302,93 +2580,120 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <f>Calibration!$E$36</f>
+        <v>135515</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <f>Calibration!$E$36</f>
+        <v>135515</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <f>Calibration!$E$37</f>
+        <v>90135.000000000233</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <f>Calibration!$E$38</f>
+        <v>137324</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <f>Calibration!$E$39</f>
+        <v>149383</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <f>Calibration!$E$40</f>
+        <v>174141</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <f>Calibration!$E$41</f>
+        <v>213757</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <f>Calibration!$E$42</f>
+        <v>225666</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <f>Calibration!$E$43</f>
+        <v>221568</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <f>Calibration!$E$44</f>
+        <v>224441</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <f>Calibration!$E$45</f>
+        <v>213772</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <f>Calibration!$E$46</f>
+        <v>204982</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <f>Calibration!$E$47</f>
+        <v>164966</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <f>Calibration!$E$48</f>
+        <v>154227</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <f>Calibration!$E$49</f>
+        <v>142271</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <f>Calibration!$E$50</f>
+        <v>126957</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <f>Calibration!$E$51</f>
+        <v>112910</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <f>Calibration!$E$52</f>
+        <v>89327</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <f>Calibration!$E$53</f>
+        <v>65254</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <f>Calibration!$E$54</f>
+        <v>40393</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <f>Calibration!$E$55</f>
+        <v>14988</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <f>Calibration!$E$56</f>
+        <v>-5691</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <f>Calibration!$E$57</f>
+        <v>-30575</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <f>Calibration!$E$58</f>
+        <v>-51119</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <f>Calibration!$E$59</f>
+        <v>-77233</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <f>Calibration!$E$60</f>
+        <v>-101990</v>
       </c>
       <c r="AB2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+        <f>Calibration!$E$61</f>
+        <v>-134401</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1474,7 +2779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1560,7 +2865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1646,7 +2951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1732,7 +3037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
